--- a/test/fixtures/order-imports/arabic-excel.xlsx
+++ b/test/fixtures/order-imports/arabic-excel.xlsx
@@ -2,8 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="1" activeTab="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="الطلبات" sheetId="1" r:id="rId1"/>
+    <sheet name="ملاحظات" sheetId="1" r:id="rId1" state="hidden"/>
+    <sheet name="الطلبات" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -32,8 +36,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="00000000000"/>
+    <numFmt numFmtId="61" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +70,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,7 +406,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:A2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>لا تقرأ هذه الورقة</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>تعليمات المندوب</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,7 +446,10 @@
         <v>طريقة الدفع</v>
       </c>
       <c r="F1" t="str">
-        <v>المدينة</v>
+        <v>تاريخ الطلب</v>
+      </c>
+      <c r="G1" t="str">
+        <v>المحافظة</v>
       </c>
     </row>
     <row r="2">
@@ -426,16 +459,20 @@
       <c r="B2" t="str">
         <v>أحمد علي</v>
       </c>
-      <c r="C2" t="str">
-        <v>01001234567</v>
+      <c r="C2" s="1">
+        <v>1001234567</v>
       </c>
       <c r="D2">
+        <f>100*2.5</f>
         <v>250</v>
       </c>
       <c r="E2" t="str">
         <v>الدفع عند الاستلام</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F2" s="2">
+        <v>46282</v>
+      </c>
+      <c r="G2" t="str">
         <v>القاهرة</v>
       </c>
     </row>
@@ -446,8 +483,8 @@
       <c r="B3" t="str">
         <v>منى حسن</v>
       </c>
-      <c r="C3" t="str">
-        <v>01112223334</v>
+      <c r="C3">
+        <v>1112223334</v>
       </c>
       <c r="D3">
         <v>99.5</v>
@@ -455,13 +492,158 @@
       <c r="E3" t="str">
         <v>كاش</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F3" s="2">
+        <v>46283</v>
+      </c>
+      <c r="G3" t="str">
         <v>الجيزة</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>سارة مصطفى</v>
+      </c>
+      <c r="C4" t="str">
+        <v>01234567890</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1250.5</v>
+      </c>
+      <c r="E4" t="str">
+        <v>عند الاستلام</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46281</v>
+      </c>
+      <c r="G4" t="str">
+        <v>الإسكندرية</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>محمد حسن</v>
+      </c>
+      <c r="C5" t="str">
+        <v>0223456789</v>
+      </c>
+      <c r="D5">
+        <v>400</v>
+      </c>
+      <c r="E5" t="str">
+        <v>الدفع عند الاستلام</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46282</v>
+      </c>
+      <c r="G5" t="str">
+        <v>القاهرة</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ياسمين عادل</v>
+      </c>
+      <c r="C6" t="str">
+        <v>01555123456</v>
+      </c>
+      <c r="D6">
+        <v>500</v>
+      </c>
+      <c r="E6" t="str">
+        <v>مدفوع</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46283</v>
+      </c>
+      <c r="G6" t="str">
+        <v>الجيزة</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>عمر خالد</v>
+      </c>
+      <c r="C7" t="str">
+        <v>01099988877</v>
+      </c>
+      <c r="D7">
+        <v>300</v>
+      </c>
+      <c r="E7" t="str">
+        <v>الدفع عند الاستلام</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G7" t="str">
+        <v>طنطا</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sara Mostafa</v>
+      </c>
+      <c r="C8" t="str">
+        <v>01011122233</v>
+      </c>
+      <c r="D8">
+        <f>SUM(700,50)</f>
+        <v>750</v>
+      </c>
+      <c r="E8" t="str">
+        <v>COD</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46284</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Cairo</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>أحمد علي</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1001234567</v>
+      </c>
+      <c r="D9">
+        <v>250</v>
+      </c>
+      <c r="E9" t="str">
+        <v>الدفع عند الاستلام</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46282</v>
+      </c>
+      <c r="G9" t="str">
+        <v>القاهرة</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G2:G3"/>
+  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>